--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -26384,7 +26384,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -50043,7 +50043,7 @@
           <t>G | 494呎 (2房)
 $1487万
 $30,105/呎
-(26年-08月-24日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -22447,7 +22447,7 @@
         </is>
       </c>
       <c r="E347" s="4" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>4087000</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>16547</v>
+        <v>16614</v>
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>4087000</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>16547</v>
+        <v>16614</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -49307,9 +49307,9 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>E | 247呎 (开放式)
+          <t>E | 246呎 (开放式)
 $409万
-$16,547/呎
+$16,614/呎
 (25年-07月-07日)</t>
         </is>
       </c>
@@ -49759,7 +49759,7 @@
           <t>C | 244呎 (开放式)
 $574万
 $23,525/呎
-(26年-06月-20日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -23421,7 +23421,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -23430,10 +23430,10 @@
         </is>
       </c>
       <c r="H362" s="5" t="n">
-        <v>5797000</v>
+        <v>6810000</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>23758</v>
+        <v>27910</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
@@ -23441,10 +23441,10 @@
         </is>
       </c>
       <c r="K362" s="5" t="n">
-        <v>5217300</v>
+        <v>6129000</v>
       </c>
       <c r="L362" s="5" t="n">
-        <v>21382</v>
+        <v>25119</v>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G369" s="3" t="inlineStr">
@@ -23888,10 +23888,10 @@
         </is>
       </c>
       <c r="H369" s="5" t="n">
-        <v>5740000</v>
+        <v>6742000</v>
       </c>
       <c r="I369" s="5" t="n">
-        <v>23525</v>
+        <v>27631</v>
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
@@ -23899,10 +23899,10 @@
         </is>
       </c>
       <c r="K369" s="5" t="n">
-        <v>5166000</v>
+        <v>6067800</v>
       </c>
       <c r="L369" s="5" t="n">
-        <v>21172</v>
+        <v>24868</v>
       </c>
       <c r="M369" s="3" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G453" s="3" t="inlineStr">
@@ -29376,10 +29376,10 @@
         </is>
       </c>
       <c r="H453" s="5" t="n">
-        <v>5300000</v>
+        <v>6506000</v>
       </c>
       <c r="I453" s="5" t="n">
-        <v>21721</v>
+        <v>26664</v>
       </c>
       <c r="J453" s="3" t="inlineStr">
         <is>
@@ -29387,10 +29387,10 @@
         </is>
       </c>
       <c r="K453" s="5" t="n">
-        <v>4770000</v>
+        <v>5855400</v>
       </c>
       <c r="L453" s="5" t="n">
-        <v>19549</v>
+        <v>23998</v>
       </c>
       <c r="M453" s="3" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
@@ -29826,10 +29826,10 @@
         </is>
       </c>
       <c r="H460" s="5" t="n">
-        <v>5273000</v>
+        <v>6468000</v>
       </c>
       <c r="I460" s="5" t="n">
-        <v>21611</v>
+        <v>26508</v>
       </c>
       <c r="J460" s="3" t="inlineStr">
         <is>
@@ -29837,10 +29837,10 @@
         </is>
       </c>
       <c r="K460" s="5" t="n">
-        <v>4745700</v>
+        <v>5821200</v>
       </c>
       <c r="L460" s="5" t="n">
-        <v>19450</v>
+        <v>23857</v>
       </c>
       <c r="M460" s="3" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
       </c>
       <c r="F467" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G467" s="3" t="inlineStr">
@@ -30276,10 +30276,10 @@
         </is>
       </c>
       <c r="H467" s="5" t="n">
-        <v>5247000</v>
+        <v>6431000</v>
       </c>
       <c r="I467" s="5" t="n">
-        <v>21504</v>
+        <v>26357</v>
       </c>
       <c r="J467" s="3" t="inlineStr">
         <is>
@@ -30287,10 +30287,10 @@
         </is>
       </c>
       <c r="K467" s="5" t="n">
-        <v>4722300</v>
+        <v>5787900</v>
       </c>
       <c r="L467" s="5" t="n">
-        <v>19354</v>
+        <v>23721</v>
       </c>
       <c r="M467" s="3" t="inlineStr">
         <is>
@@ -49477,12 +49477,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -49565,12 +49565,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$580万
-$23,758/呎
-(已定价未售)</t>
+$681万
+$27,910/呎
+(在售)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -49628,12 +49628,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$574万
-$23,525/呎
-(已定价未售)</t>
+$674万
+$27,631/呎
+(在售)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -50384,12 +50384,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$530万
-$21,721/呎
-(已定价未售)</t>
+$651万
+$26,664/呎
+(在售)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -50447,12 +50447,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$527万
-$21,611/呎
-(已定价未售)</t>
+$647万
+$26,508/呎
+(在售)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -50510,12 +50510,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>C | 244呎 (开放式)
-$525万
-$21,504/呎
-(已定价未售)</t>
+$643万
+$26,357/呎
+(在售)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -33422,7 +33422,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -50956,7 +50956,7 @@
           <t>C | 244呎 (开放式)
 $541万
 $22,184/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">

--- a/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
+++ b/九龙-启德-维港．双钻/维港．双钻_销控明细表.xlsx
@@ -24800,7 +24800,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -49759,7 +49759,7 @@
           <t>C | 244呎 (开放式)
 $574万
 $23,525/呎
-(26年-09月-10日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
